--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 05 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 06 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 06 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 08 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 08 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 09 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 09 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 10 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 10 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 11 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 11 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 12 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 12 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 14 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 14 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 15 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 15 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 16 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 16 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 17 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 17 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 18 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 18 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 19 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 19 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 20 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 20 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 21 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 21 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 23 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 23 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 24 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 24 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 25 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 25 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 26 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 26 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 27 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 27 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 28 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 28 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 29 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="L353" s="12" t="inlineStr">
         <is>
-          <t>Darebin Womens SC U13</t>
+          <t>Darebin Falcons Womens SC U13</t>
         </is>
       </c>
       <c r="M353" s="12" t="inlineStr">
@@ -27391,7 +27391,7 @@
       </c>
       <c r="L354" s="10" t="inlineStr">
         <is>
-          <t>Darebin Womens SC U15</t>
+          <t>Darebin Falcons Womens SC U15</t>
         </is>
       </c>
       <c r="M354" s="10" t="inlineStr">
@@ -27468,7 +27468,7 @@
       </c>
       <c r="L355" s="12" t="inlineStr">
         <is>
-          <t>Darebin Womens SC U17</t>
+          <t>Darebin Falcons Womens SC U17</t>
         </is>
       </c>
       <c r="M355" s="12" t="inlineStr">
@@ -44462,7 +44462,7 @@
       </c>
       <c r="L577" s="12" t="inlineStr">
         <is>
-          <t>Darebin Womens SC U09 MiniRoos - Wallabies Female Darebin Falcons Red</t>
+          <t>Darebin Falcons Womens SC U09 MiniRoos - Wallabies Female Darebin Falcons Red</t>
         </is>
       </c>
       <c r="M577" s="12" t="inlineStr">

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 29 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 30 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 30 Sep 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 01 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 01 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 02 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 02 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 03 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 03 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 04 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 04 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 05 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 05 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 06 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 06 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 07 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 07 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 08 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 08 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 09 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 09 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 10 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 10 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 11 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 11 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 12 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 12 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 13 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 13 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 14 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 14 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 15 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 15 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 16 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 16 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 17 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 17 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 18 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 18 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 19 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 19 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 20 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 20 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 21 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 21 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 22 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 22 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 23 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 23 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 24 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 24 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 25 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 25 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 26 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 26 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 27 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 27 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 28 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 28 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 29 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 29 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 30 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/Manningham_fixtures_and_overlaps.xlsx
+++ b/Manningham_fixtures_and_overlaps.xlsx
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: fv.dribl.com, 2026 season, generated 30 Oct 2026</t>
+          <t>Source: fv.dribl.com, 2026 season, generated 31 Oct 2026</t>
         </is>
       </c>
     </row>
